--- a/data/trans_camb/P1802_2016_2023-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1802_2016_2023-Edad-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-2,61</t>
+          <t>-2,49</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-3,43</t>
+          <t>-2,01</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-3,17</t>
+          <t>-2,33</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 3,27</t>
+          <t>-6,87; 3,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 2,36</t>
+          <t>-7,43; 4,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 0,9</t>
+          <t>-6,21; 1,63</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-25,43%</t>
+          <t>-24,24%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-23,49%</t>
+          <t>-13,79%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-25,64%</t>
+          <t>-18,83%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-64,88; 44,66</t>
+          <t>-59,57; 41,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-54,09; 19,39</t>
+          <t>-44,85; 40,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-49,15; 9,02</t>
+          <t>-45,39; 14,11</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-1,15</t>
+          <t>-1,97</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-5,04</t>
+          <t>-3,99</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-3,05</t>
+          <t>-2,92</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 3,42</t>
+          <t>-6,12; 2,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,29; -0,83</t>
+          <t>-7,98; -0,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 0,52</t>
+          <t>-5,93; 0,03</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-10,07%</t>
+          <t>-17,28%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-33,11%</t>
+          <t>-26,25%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-23,01%</t>
+          <t>-21,98%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-43,58; 35,5</t>
+          <t>-47,14; 29,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-59,68; -6,27</t>
+          <t>-47,27; -0,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,75; 4,49</t>
+          <t>-41,42; -0,74</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4,51</t>
+          <t>2,37</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,13</t>
+          <t>0,92</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 9,12</t>
+          <t>-1,83; 6,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 3,19</t>
+          <t>-4,17; 3,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 5,16</t>
+          <t>-1,68; 3,84</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-1,62%</t>
+          <t>-3,47%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,77; 79,98</t>
+          <t>-12,12; 53,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 23,87</t>
+          <t>-23,86; 22,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 38,95</t>
+          <t>-10,72; 30,11</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>23,04</t>
+          <t>-0,6</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4,11</t>
+          <t>5,38</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14,64</t>
+          <t>2,46</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 57,99</t>
+          <t>-5,01; 3,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 7,98</t>
+          <t>1,27; 8,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 43,52</t>
+          <t>-0,51; 5,23</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>137,75%</t>
+          <t>-3,56%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 366,74</t>
+          <t>-26,19; 22,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 58,04</t>
+          <t>7,02; 64,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,57; 269,45</t>
+          <t>-2,6; 35,42</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>5,21</t>
+          <t>4,42</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>-0,2</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,38</t>
+          <t>2,01</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 10,06</t>
+          <t>-0,26; 9,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 4,65</t>
+          <t>-5,76; 4,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 5,69</t>
+          <t>-1,27; 5,39</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-0,71%</t>
+          <t>-0,78%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1,76; 80,27</t>
+          <t>-2,16; 70,58</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 20,63</t>
+          <t>-19,36; 19,93</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 30,13</t>
+          <t>-5,78; 28,29</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2,21</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-10,63</t>
+          <t>-3,34</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-5,05</t>
+          <t>-1,04</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 7,55</t>
+          <t>-4,01; 6,77</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-22,77; -1,77</t>
+          <t>-8,6; 2,06</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 0,55</t>
+          <t>-4,46; 2,93</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-42,97%</t>
+          <t>-13,51%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-24,08%</t>
+          <t>-4,98%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 55,2</t>
+          <t>-18,7; 51,99</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-77,83; -7,14</t>
+          <t>-30,13; 9,86</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-62,92; 2,64</t>
+          <t>-19,68; 16,42</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-2,3</t>
+          <t>-2,85</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-3,27</t>
+          <t>-3,29</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-2,92</t>
+          <t>-3,16</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 3,77</t>
+          <t>-8,78; 2,62</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 2,19</t>
+          <t>-9,29; 1,56</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 0,94</t>
+          <t>-7,18; 0,65</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-12,47%</t>
+          <t>-15,48%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-13,73%</t>
+          <t>-13,79%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-13,47%</t>
+          <t>-14,56%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-37,23; 24,8</t>
+          <t>-39,86; 17,35</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-32,01; 11,75</t>
+          <t>-33,38; 7,64</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-31,06; 4,74</t>
+          <t>-29,47; 4,31</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>7,51</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-1,7</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>0,31</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,02; 25,54</t>
+          <t>-0,88; 2,57</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 0,43</t>
+          <t>-1,81; 1,54</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 13,81</t>
+          <t>-1,02; 1,48</t>
         </is>
       </c>
     </row>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-8,99%</t>
+          <t>-0,7%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>7,26; 187,07</t>
+          <t>-5,78; 18,89</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-24,92; 2,33</t>
+          <t>-9,08; 8,54</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 86,93</t>
+          <t>-5,73; 9,3</t>
         </is>
       </c>
     </row>
